--- a/backend/data/financials_by_company/002510.SZ.xlsx
+++ b/backend/data/financials_by_company/002510.SZ.xlsx
@@ -4050,197 +4050,197 @@
       </c>
       <c r="DI1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="EV1" t="inlineStr">
@@ -4252,7 +4252,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tianjin Airport Economic Zone</t>
+          <t>Tianjin Free Trade Zone (Airport Economic Zone)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4277,12 +4277,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>86 22 2489 5297</t>
+          <t>86 22 2489 0729</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>86 22 2489 5279</t>
+          <t>86 22 2489 6985</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Tianjin Motor Dies Co.,Ltd. engages in the research and development, design, production, and sale of automobile body panel molds and supporting products in China and internationally. The company offers automobile body panel molds, automobile body stamping parts, inspection tools, and welding fixtures; and aviation parts. Tianjin Motor Dies Co., Ltd. was founded in 1996 and is headquartered in Tianjin, China.</t>
+          <t>Tianjin Motor Dies Co.,Ltd., together with its subsidiaries, engages in the research, design, production, and sale of automotive body panel molds and related products in China and internationally. The company offers automotive body panel molds and stamping parts, inspection tools, and welding fixtures; aviation parts; stamping parts and welding; electronic and communication equipment; and vehicle process equipment. It also provides technical consulting, computer application, import and export, and software development services. Tianjin Motor Dies Co., Ltd. was founded in 1996 and is headquartered in Tianjin, China.</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4345,34 +4345,34 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>6.18</v>
+        <v>5.77</v>
       </c>
       <c r="V2" t="n">
-        <v>6.06</v>
+        <v>5.88</v>
       </c>
       <c r="W2" t="n">
-        <v>5.91</v>
+        <v>5.71</v>
       </c>
       <c r="X2" t="n">
-        <v>6.14</v>
+        <v>5.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.18</v>
+        <v>5.77</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.06</v>
+        <v>5.88</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.91</v>
+        <v>5.71</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.14</v>
+        <v>5.9</v>
       </c>
       <c r="AC2" t="n">
         <v>0.03</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="AE2" t="n">
         <v>1752019200</v>
@@ -4384,34 +4384,34 @@
         <v>0.71</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.435</v>
+        <v>0.455</v>
       </c>
       <c r="AI2" t="n">
-        <v>120.4</v>
+        <v>115.600006</v>
       </c>
       <c r="AJ2" t="n">
-        <v>20.066666</v>
+        <v>19.266666</v>
       </c>
       <c r="AK2" t="n">
-        <v>23735636</v>
+        <v>23728127</v>
       </c>
       <c r="AL2" t="n">
-        <v>23735636</v>
+        <v>23728127</v>
       </c>
       <c r="AM2" t="n">
-        <v>28692207</v>
+        <v>28683601</v>
       </c>
       <c r="AN2" t="n">
-        <v>29819552</v>
+        <v>25511291</v>
       </c>
       <c r="AO2" t="n">
-        <v>29819552</v>
+        <v>25511291</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.01</v>
+        <v>5.78</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.02</v>
+        <v>5.79</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -4420,13 +4420,13 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>6111134720</v>
+        <v>5867502080</v>
       </c>
       <c r="AU2" t="n">
-        <v>6273557215</v>
+        <v>5776139248</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.91</v>
+        <v>5.22</v>
       </c>
       <c r="AW2" t="n">
         <v>9.09</v>
@@ -4438,13 +4438,13 @@
         <v>1.975</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.5286798</v>
+        <v>2.4278688</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.7904</v>
+        <v>6.556</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.1682</v>
+        <v>7.1133</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
@@ -4461,13 +4461,13 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>6628164096</v>
+        <v>6384530944</v>
       </c>
       <c r="BH2" t="n">
         <v>0.02476</v>
       </c>
       <c r="BI2" t="n">
-        <v>751974149</v>
+        <v>757242719</v>
       </c>
       <c r="BJ2" t="n">
         <v>1015138708</v>
@@ -4485,7 +4485,7 @@
         <v>2.497</v>
       </c>
       <c r="BO2" t="n">
-        <v>2.4108932</v>
+        <v>2.3147779</v>
       </c>
       <c r="BP2" t="n">
         <v>1767139200</v>
@@ -4517,16 +4517,16 @@
         <v>1461888000</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.743</v>
+        <v>2.642</v>
       </c>
       <c r="BZ2" t="n">
-        <v>55.526</v>
+        <v>53.485</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0.03888023</v>
+        <v>-0.13233083</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="CC2" t="n">
         <v>0.03</v>
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="CF2" t="n">
-        <v>6.02</v>
+        <v>5.78</v>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
@@ -4642,150 +4642,150 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DI2" t="n">
-        <v>-0.15999985</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>5.91 - 6.14</t>
-        </is>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DJ2" t="n">
+        <v>1783062294</v>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>finmb_47065418</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="DP2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>Tianjin Motor Dies Co.,Ltd.</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>TIANJIN MOTOR DIES CO LTD</t>
+        </is>
+      </c>
+      <c r="DT2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-0.776</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-0.118364856</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-1.3332996</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.18743756</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>Tianjin Motor Dies Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="EE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>0.1733142</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="EH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>1290648600000</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>0.010000229</v>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>5.71 - 5.9</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
           <t>Shenzhen</t>
         </is>
       </c>
-      <c r="DL2" t="n">
-        <v>28692207</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0.11000013</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0.018612545</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>5.91 - 9.09</t>
-        </is>
-      </c>
-      <c r="DP2" t="n">
-        <v>-3.0700002</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0.33773378</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-3.888023</v>
-      </c>
-      <c r="DS2" t="n">
+      <c r="EM2" t="n">
+        <v>28683601</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>0.5600004</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>0.10727978</v>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>5.22 - 9.09</t>
+        </is>
+      </c>
+      <c r="EQ2" t="n">
+        <v>-3.31</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>-0.3641364</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>-13.233084</v>
+      </c>
+      <c r="ET2" t="n">
         <v>1619607540</v>
       </c>
-      <c r="DT2" t="n">
+      <c r="EU2" t="n">
         <v>1619607540</v>
-      </c>
-      <c r="DU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>1290648600000</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-2.5889945</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>6.02</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.77040005</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.1134543</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-1.1482</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>-0.16017969</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>Tianjin Motor Dies Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EK2" t="n">
-        <v>1782111885</v>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>finmb_47065418</t>
-        </is>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="EP2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="ER2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
-          <t>TIANJIN MOTOR DIES CO LTD</t>
-        </is>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>Tianjin Motor Dies Co.,Ltd.</t>
-        </is>
-      </c>
-      <c r="EU2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
       </c>
       <c r="EV2" t="inlineStr"/>
     </row>
